--- a/daily_matches/job_matches_2026-04-12.xlsx
+++ b/daily_matches/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Cross and Blue Shield of Minnesota</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Athena, Redshift, Kinesis, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Keras, S3, Glue, Athena</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,497 +496,112 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e68aed4fb5428da</t>
+          <t>https://www.indeed.com/viewjob?jk=a49a54c48156d9f6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Senior Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dexmate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Glue, MLflow, Docker</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4de601df807639</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Glue, MLflow, Docker</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Hadoop, Tableau, Power BI, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
+          <t>https://www.indeed.com/viewjob?jk=9093fc6773f5624b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer - Applied AI (Java)</t>
+          <t>Data Scientist / ML Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Infotron</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71098c13621f053</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Applied AI (Java)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3edd7e2e5d67cfb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Applied AI (Java)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e515a5d806b8ccd</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Applied AI (Java)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e50beaa16a5c382a</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Applied AI (Java)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5fc52ccc594b09</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Consultant Azure AI Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Larouche Raymond Firme-Conseil en Ressources Humaines Inc.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Synapse, Data Lake, Terraform, Git, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15c38867b28c314f</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fortinet SD-WAN Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Copilot, AKS, CI/CD, Git, Snowflake, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98393b868b60735c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>data scientist</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Snowflake, Hadoop, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b8e71e0ba83ff5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Adv Eng, SIP</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Invesco</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8ad016ffd21593</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Network IoT Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, BigQuery, Dataflow, Git, BigQuery, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30b261f736a09186</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Applied Scientist</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>THRAD</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PyTorch, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=803c2aa38744679d</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AI Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>AR5 Labs</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, LangChain, Gemini, Prompt Engineering, FastAPI, Git, Python, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5159af25afd3400</t>
+          <t>https://www.indeed.com/viewjob?jk=f7c74baff6b81028</t>
         </is>
       </c>
     </row>
